--- a/tools/importer/reports/import-medicare.report.xlsx
+++ b/tools/importer/reports/import-medicare.report.xlsx
@@ -73,7 +73,7 @@
     <t>medicare</t>
   </si>
   <si>
-    <t>2026-09-03T20:46:05.594Z</t>
+    <t>2026-09-03T20:49:22.981Z</t>
   </si>
   <si>
     <t>Shop 2026 Medicare Advantage Plans near you: Extra Benefits &amp; Coverages | HealthSpring</t>
